--- a/samples/family-medicine.xlsx
+++ b/samples/family-medicine.xlsx
@@ -397,149 +397,185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>اسم المديرية</v>
+      </c>
+      <c r="B1" t="str">
+        <v>اسم المركز الصحي</v>
+      </c>
+      <c r="C1" t="str">
         <v>اسم المراجع</v>
       </c>
-      <c r="B1" t="str">
+      <c r="D1" t="str">
         <v>رقم الهوية</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>موعد الحجز</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>وقت الحجز</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>اسم الطبيب</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>اسم التخصص</v>
       </c>
-      <c r="G1" t="str">
-        <v>رقم الاتصال</v>
+      <c r="I1" t="str">
+        <v>رقم الجوال</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>مديرية الشؤون الصحية بالرياض</v>
+      </c>
+      <c r="B2" t="str">
+        <v>مركز صحي النخيل</v>
+      </c>
+      <c r="C2" t="str">
         <v>محمد أحمد الغامدي</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D2" t="str">
         <v>1012345678</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E2" t="str">
         <v>2026-08-12</v>
       </c>
-      <c r="D2" t="str">
+      <c r="F2" t="str">
         <v>09:00</v>
       </c>
-      <c r="E2" t="str">
+      <c r="G2" t="str">
         <v>د. سعاد المطيري</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>0501234567</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>مديرية الشؤون الصحية بالرياض</v>
+      </c>
+      <c r="B3" t="str">
+        <v>مركز صحي النخيل</v>
+      </c>
+      <c r="C3" t="str">
         <v>نورة سعد القحطاني</v>
       </c>
-      <c r="B3" t="str">
+      <c r="D3" t="str">
         <v>1023456789</v>
       </c>
-      <c r="C3" t="str">
+      <c r="E3" t="str">
         <v>2026-08-12</v>
       </c>
-      <c r="D3" t="str">
+      <c r="F3" t="str">
         <v>09:30</v>
       </c>
-      <c r="E3" t="str">
+      <c r="G3" t="str">
         <v>د. خالد العتيبي</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>0552345678</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>مديرية الشؤون الصحية بالرياض</v>
+      </c>
+      <c r="B4" t="str">
+        <v>مركز صحي العليا</v>
+      </c>
+      <c r="C4" t="str">
         <v>عبدالله فهد الشهري</v>
       </c>
-      <c r="B4" t="str">
+      <c r="D4" t="str">
         <v>1034567890</v>
       </c>
-      <c r="C4" t="str">
+      <c r="E4" t="str">
         <v>2026-08-12</v>
       </c>
-      <c r="D4" t="str">
+      <c r="F4" t="str">
         <v>10:00</v>
       </c>
-      <c r="E4" t="str">
+      <c r="G4" t="str">
         <v>د. سعاد المطيري</v>
       </c>
-      <c r="F4" t="str">
+      <c r="H4" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>0533456789</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>مديرية الشؤون الصحية بالرياض</v>
+      </c>
+      <c r="B5" t="str">
+        <v>مركز صحي العليا</v>
+      </c>
+      <c r="C5" t="str">
         <v>ريم ناصر الدوسري</v>
       </c>
-      <c r="B5" t="str">
+      <c r="D5" t="str">
         <v>1045678901</v>
       </c>
-      <c r="C5" t="str">
+      <c r="E5" t="str">
         <v>2026-08-13</v>
       </c>
-      <c r="D5" t="str">
+      <c r="F5" t="str">
         <v>10:30</v>
       </c>
-      <c r="E5" t="str">
+      <c r="G5" t="str">
         <v>د. خالد العتيبي</v>
       </c>
-      <c r="F5" t="str">
+      <c r="H5" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>0544567890</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>مديرية الشؤون الصحية بالرياض</v>
+      </c>
+      <c r="B6" t="str">
+        <v>مركز صحي الملز</v>
+      </c>
+      <c r="C6" t="str">
         <v>سلطان عمر الحربي</v>
       </c>
-      <c r="B6" t="str">
+      <c r="D6" t="str">
         <v>1056789012</v>
       </c>
-      <c r="C6" t="str">
+      <c r="E6" t="str">
         <v>2026-08-13</v>
       </c>
-      <c r="D6" t="str">
+      <c r="F6" t="str">
         <v>11:00</v>
       </c>
-      <c r="E6" t="str">
+      <c r="G6" t="str">
         <v>د. منى الزهراني</v>
       </c>
-      <c r="F6" t="str">
+      <c r="H6" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>0565678901</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/family-medicine.xlsx
+++ b/samples/family-medicine.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,15 +416,18 @@
         <v>موعد الحجز</v>
       </c>
       <c r="F1" t="str">
-        <v>وقت الحجز</v>
+        <v>وقت بداية الموعد</v>
       </c>
       <c r="G1" t="str">
+        <v>تاريخ وصول المراجع</v>
+      </c>
+      <c r="H1" t="str">
         <v>اسم الطبيب</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>اسم التخصص</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>رقم الجوال</v>
       </c>
     </row>
@@ -448,12 +451,15 @@
         <v>09:00</v>
       </c>
       <c r="G2" t="str">
+        <v>2026-08-12</v>
+      </c>
+      <c r="H2" t="str">
         <v>د. سعاد المطيري</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>0501234567</v>
       </c>
     </row>
@@ -477,12 +483,15 @@
         <v>09:30</v>
       </c>
       <c r="G3" t="str">
+        <v>2026-08-12</v>
+      </c>
+      <c r="H3" t="str">
         <v>د. خالد العتيبي</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>0552345678</v>
       </c>
     </row>
@@ -506,12 +515,15 @@
         <v>10:00</v>
       </c>
       <c r="G4" t="str">
+        <v>2026-08-12</v>
+      </c>
+      <c r="H4" t="str">
         <v>د. سعاد المطيري</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>0533456789</v>
       </c>
     </row>
@@ -535,12 +547,15 @@
         <v>10:30</v>
       </c>
       <c r="G5" t="str">
+        <v>2026-08-13</v>
+      </c>
+      <c r="H5" t="str">
         <v>د. خالد العتيبي</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>0544567890</v>
       </c>
     </row>
@@ -564,18 +579,21 @@
         <v>11:00</v>
       </c>
       <c r="G6" t="str">
+        <v>2026-08-13</v>
+      </c>
+      <c r="H6" t="str">
         <v>د. منى الزهراني</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>طب الأسرة</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>0565678901</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/family-medicine.xlsx
+++ b/samples/family-medicine.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:I6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,18 +416,15 @@
         <v>موعد الحجز</v>
       </c>
       <c r="F1" t="str">
-        <v>وقت بداية الموعد</v>
+        <v>تاريخ وصول المراجع</v>
       </c>
       <c r="G1" t="str">
-        <v>تاريخ وصول المراجع</v>
+        <v>اسم الطبيب</v>
       </c>
       <c r="H1" t="str">
-        <v>اسم الطبيب</v>
+        <v>اسم التخصص</v>
       </c>
       <c r="I1" t="str">
-        <v>اسم التخصص</v>
-      </c>
-      <c r="J1" t="str">
         <v>رقم الجوال</v>
       </c>
     </row>
@@ -448,18 +445,15 @@
         <v>2026-08-12</v>
       </c>
       <c r="F2" t="str">
-        <v>09:00</v>
+        <v>2026-08-12</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-12</v>
+        <v>د. سعاد المطيري</v>
       </c>
       <c r="H2" t="str">
-        <v>د. سعاد المطيري</v>
+        <v>طب الأسرة</v>
       </c>
       <c r="I2" t="str">
-        <v>طب الأسرة</v>
-      </c>
-      <c r="J2" t="str">
         <v>0501234567</v>
       </c>
     </row>
@@ -480,18 +474,15 @@
         <v>2026-08-12</v>
       </c>
       <c r="F3" t="str">
-        <v>09:30</v>
+        <v>2026-08-12</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-12</v>
+        <v>د. خالد العتيبي</v>
       </c>
       <c r="H3" t="str">
-        <v>د. خالد العتيبي</v>
+        <v>طب الأسرة</v>
       </c>
       <c r="I3" t="str">
-        <v>طب الأسرة</v>
-      </c>
-      <c r="J3" t="str">
         <v>0552345678</v>
       </c>
     </row>
@@ -512,18 +503,15 @@
         <v>2026-08-12</v>
       </c>
       <c r="F4" t="str">
-        <v>10:00</v>
+        <v>2026-08-12</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-12</v>
+        <v>د. سعاد المطيري</v>
       </c>
       <c r="H4" t="str">
-        <v>د. سعاد المطيري</v>
+        <v>طب الأسرة</v>
       </c>
       <c r="I4" t="str">
-        <v>طب الأسرة</v>
-      </c>
-      <c r="J4" t="str">
         <v>0533456789</v>
       </c>
     </row>
@@ -544,18 +532,15 @@
         <v>2026-08-13</v>
       </c>
       <c r="F5" t="str">
-        <v>10:30</v>
+        <v>2026-08-13</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-13</v>
+        <v>د. خالد العتيبي</v>
       </c>
       <c r="H5" t="str">
-        <v>د. خالد العتيبي</v>
+        <v>طب الأسرة</v>
       </c>
       <c r="I5" t="str">
-        <v>طب الأسرة</v>
-      </c>
-      <c r="J5" t="str">
         <v>0544567890</v>
       </c>
     </row>
@@ -576,24 +561,21 @@
         <v>2026-08-13</v>
       </c>
       <c r="F6" t="str">
-        <v>11:00</v>
+        <v>2026-08-13</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-13</v>
+        <v>د. منى الزهراني</v>
       </c>
       <c r="H6" t="str">
-        <v>د. منى الزهراني</v>
+        <v>طب الأسرة</v>
       </c>
       <c r="I6" t="str">
-        <v>طب الأسرة</v>
-      </c>
-      <c r="J6" t="str">
         <v>0565678901</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/family-medicine.xlsx
+++ b/samples/family-medicine.xlsx
@@ -416,7 +416,7 @@
         <v>موعد الحجز</v>
       </c>
       <c r="F1" t="str">
-        <v>وقت الحجز</v>
+        <v>وقت بداية الموعد</v>
       </c>
       <c r="G1" t="str">
         <v>اسم الطبيب</v>
